--- a/新商品清单_20260828.xlsx
+++ b/新商品清单_20260828.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新商品" sheetId="1" r:id="R22f3f1c3ff68415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新商品" sheetId="1" r:id="R7c65cdc71926494c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,386 +333,386 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="6" t="n">
+      <x:c r="A2" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
+      <x:c r="B2" s="10" t="str">
         <x:v>6878#</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str">
+      <x:c r="C2" s="8" t="str">
         <x:v>L-XXXL</x:v>
       </x:c>
-      <x:c r="D2" s="7" t="n">
+      <x:c r="D2" s="9" t="n">
         <x:v>115000</x:v>
       </x:c>
-      <x:c r="E2" s="7" t="n">
+      <x:c r="E2" s="9" t="n">
         <x:f>D2/10</x:f>
         <x:v>11500</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="str">
+      <x:c r="F2" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.35 PM (1).jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="6" t="n">
+      <x:c r="A3" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="6" t="str">
+      <x:c r="B3" s="10" t="str">
         <x:v>6227#</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="str">
+      <x:c r="C3" s="8" t="str">
         <x:v>M—XXL</x:v>
       </x:c>
-      <x:c r="D3" s="7" t="n">
+      <x:c r="D3" s="9" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="E3" s="7" t="n">
+      <x:c r="E3" s="9" t="n">
         <x:f>D3/10</x:f>
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F3" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="str">
+      <x:c r="F3" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.35 PM (2).jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="6" t="n">
+      <x:c r="A4" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="6" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>968#</x:v>
       </x:c>
-      <x:c r="C4" s="6" t="str">
+      <x:c r="C4" s="8" t="str">
         <x:v>XL-XXXL</x:v>
       </x:c>
-      <x:c r="D4" s="7" t="n">
+      <x:c r="D4" s="9" t="n">
         <x:v>130000</x:v>
       </x:c>
-      <x:c r="E4" s="7" t="n">
+      <x:c r="E4" s="9" t="n">
         <x:f>D4/10</x:f>
         <x:v>13000</x:v>
       </x:c>
-      <x:c r="F4" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G4" s="6" t="str">
+      <x:c r="F4" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G4" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.35 PM.jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="6" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="str">
+      <x:c r="B5" s="10" t="str">
         <x:v>94397#</x:v>
       </x:c>
-      <x:c r="C5" s="6" t="str">
+      <x:c r="C5" s="8" t="str">
         <x:v>M—XL</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="n">
+      <x:c r="D5" s="9" t="n">
         <x:v>115000</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="n">
+      <x:c r="E5" s="9" t="n">
         <x:f>D5/10</x:f>
         <x:v>11500</x:v>
       </x:c>
-      <x:c r="F5" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G5" s="6" t="str">
+      <x:c r="F5" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.36 PM (2).jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="6" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="str">
+      <x:c r="B6" s="10" t="str">
         <x:v>7613#</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="str">
+      <x:c r="C6" s="8" t="str">
         <x:v>L-5XL</x:v>
       </x:c>
-      <x:c r="D6" s="7" t="n">
+      <x:c r="D6" s="9" t="n">
         <x:v>130000</x:v>
       </x:c>
-      <x:c r="E6" s="7" t="n">
+      <x:c r="E6" s="9" t="n">
         <x:f>D6/10</x:f>
         <x:v>13000</x:v>
       </x:c>
-      <x:c r="F6" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="str">
+      <x:c r="F6" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.36 PM (3).jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="6" t="n">
+      <x:c r="A7" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="6" t="str">
+      <x:c r="B7" s="10" t="str">
         <x:v>004#</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C7" s="8" t="str">
         <x:v>L—3XL</x:v>
       </x:c>
-      <x:c r="D7" s="7" t="n">
+      <x:c r="D7" s="9" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="E7" s="7" t="n">
+      <x:c r="E7" s="9" t="n">
         <x:f>D7/10</x:f>
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F7" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="str">
+      <x:c r="F7" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.36 PM (4).jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="6" t="n">
+      <x:c r="A8" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="B8" s="10" t="str">
         <x:v>6657#</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C8" s="8" t="str">
         <x:v>M—2XL</x:v>
       </x:c>
-      <x:c r="D8" s="7" t="n">
+      <x:c r="D8" s="9" t="n">
         <x:v>115000</x:v>
       </x:c>
-      <x:c r="E8" s="7" t="n">
+      <x:c r="E8" s="9" t="n">
         <x:f>D8/10</x:f>
         <x:v>11500</x:v>
       </x:c>
-      <x:c r="F8" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G8" s="6" t="str">
+      <x:c r="F8" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.36 PM.jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="6" t="n">
+      <x:c r="A9" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="B9" s="10" t="str">
         <x:v>8839#</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C9" s="8" t="str">
         <x:v>XL—6XL</x:v>
       </x:c>
-      <x:c r="D9" s="7" t="n">
+      <x:c r="D9" s="9" t="n">
         <x:v>130000</x:v>
       </x:c>
-      <x:c r="E9" s="7" t="n">
+      <x:c r="E9" s="9" t="n">
         <x:f>D9/10</x:f>
         <x:v>13000</x:v>
       </x:c>
-      <x:c r="F9" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="str">
+      <x:c r="F9" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.37 PM (1).jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="6" t="n">
+      <x:c r="A10" s="8" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="B10" s="10" t="str">
         <x:v>6875#</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C10" s="8" t="str">
         <x:v>L-XXXL</x:v>
       </x:c>
-      <x:c r="D10" s="7" t="n">
+      <x:c r="D10" s="9" t="n">
         <x:v>115000</x:v>
       </x:c>
-      <x:c r="E10" s="7" t="n">
+      <x:c r="E10" s="9" t="n">
         <x:f>D10/10</x:f>
         <x:v>11500</x:v>
       </x:c>
-      <x:c r="F10" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G10" s="6" t="str">
+      <x:c r="F10" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G10" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.37 PM (2).jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="6" t="n">
+      <x:c r="A11" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="B11" s="10" t="str">
         <x:v>8062#</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C11" s="8" t="str">
         <x:v>M—2XL</x:v>
       </x:c>
-      <x:c r="D11" s="7" t="n">
+      <x:c r="D11" s="9" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="E11" s="7" t="n">
+      <x:c r="E11" s="9" t="n">
         <x:f>D11/10</x:f>
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F11" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G11" s="6" t="str">
+      <x:c r="F11" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.37 PM (3).jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="6" t="n">
+      <x:c r="A12" s="8" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="B12" s="10" t="str">
         <x:v>9841#</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C12" s="8" t="str">
         <x:v>L—3XL</x:v>
       </x:c>
-      <x:c r="D12" s="7" t="n">
+      <x:c r="D12" s="9" t="n">
         <x:v>130000</x:v>
       </x:c>
-      <x:c r="E12" s="7" t="n">
+      <x:c r="E12" s="9" t="n">
         <x:f>D12/10</x:f>
         <x:v>13000</x:v>
       </x:c>
-      <x:c r="F12" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G12" s="6" t="str">
+      <x:c r="F12" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.37 PM.jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="6" t="n">
+      <x:c r="A13" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B13" s="6" t="str">
+      <x:c r="B13" s="10" t="str">
         <x:v>6698#</x:v>
       </x:c>
-      <x:c r="C13" s="6" t="str">
+      <x:c r="C13" s="8" t="str">
         <x:v>L—4XL</x:v>
       </x:c>
-      <x:c r="D13" s="7" t="n">
+      <x:c r="D13" s="9" t="n">
         <x:v>130000</x:v>
       </x:c>
-      <x:c r="E13" s="7" t="n">
+      <x:c r="E13" s="9" t="n">
         <x:f>D13/10</x:f>
         <x:v>13000</x:v>
       </x:c>
-      <x:c r="F13" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G13" s="6" t="str">
+      <x:c r="F13" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.38 PM (1).jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="6" t="n">
+      <x:c r="A14" s="8" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B14" s="6" t="str">
+      <x:c r="B14" s="10" t="str">
         <x:v>9842#</x:v>
       </x:c>
-      <x:c r="C14" s="6" t="str">
+      <x:c r="C14" s="8" t="str">
         <x:v>L—3XL</x:v>
       </x:c>
-      <x:c r="D14" s="7" t="n">
+      <x:c r="D14" s="9" t="n">
         <x:v>130000</x:v>
       </x:c>
-      <x:c r="E14" s="7" t="n">
+      <x:c r="E14" s="9" t="n">
         <x:f>D14/10</x:f>
         <x:v>13000</x:v>
       </x:c>
-      <x:c r="F14" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G14" s="6" t="str">
+      <x:c r="F14" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.38 PM.jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="6" t="n">
+      <x:c r="A15" s="8" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B15" s="6" t="str">
+      <x:c r="B15" s="10" t="str">
         <x:v>HG1728#</x:v>
       </x:c>
-      <x:c r="C15" s="6" t="str">
+      <x:c r="C15" s="8" t="str">
         <x:v>L-XL-XXL-XXXL</x:v>
       </x:c>
-      <x:c r="D15" s="7" t="n">
+      <x:c r="D15" s="9" t="n">
         <x:v>200000</x:v>
       </x:c>
-      <x:c r="E15" s="7" t="n">
+      <x:c r="E15" s="9" t="n">
         <x:f>D15/10</x:f>
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="F15" s="6" t="str">
-        <x:v>文胸</x:v>
-      </x:c>
-      <x:c r="G15" s="6" t="str">
+      <x:c r="F15" s="8" t="str">
+        <x:v>文胸</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.39 PM.jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="6" t="n">
+      <x:c r="A16" s="8" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B16" s="6" t="str">
+      <x:c r="B16" s="10" t="str">
         <x:v>HW848-3Smal(小码)</x:v>
       </x:c>
-      <x:c r="C16" s="6" t="str">
+      <x:c r="C16" s="8" t="str">
         <x:v>S-M-L</x:v>
       </x:c>
-      <x:c r="D16" s="7" t="n">
+      <x:c r="D16" s="9" t="n">
         <x:v>58000</x:v>
       </x:c>
-      <x:c r="E16" s="7" t="n">
+      <x:c r="E16" s="9" t="n">
         <x:f>D16/10</x:f>
         <x:v>5800</x:v>
       </x:c>
-      <x:c r="F16" s="6" t="str">
+      <x:c r="F16" s="8" t="str">
         <x:v>束身衣</x:v>
       </x:c>
-      <x:c r="G16" s="6" t="str">
+      <x:c r="G16" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.41 PM (3).jpeg</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="6" t="n">
+      <x:c r="A17" s="8" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B17" s="6" t="str">
+      <x:c r="B17" s="10" t="str">
         <x:v>HW848-3Plus(大码)</x:v>
       </x:c>
-      <x:c r="C17" s="6" t="str">
+      <x:c r="C17" s="8" t="str">
         <x:v>XL-XXL-XXXL</x:v>
       </x:c>
-      <x:c r="D17" s="7" t="n">
+      <x:c r="D17" s="9" t="n">
         <x:v>58000</x:v>
       </x:c>
-      <x:c r="E17" s="7" t="n">
+      <x:c r="E17" s="9" t="n">
         <x:f>D17/10</x:f>
         <x:v>5800</x:v>
       </x:c>
-      <x:c r="F17" s="6" t="str">
+      <x:c r="F17" s="8" t="str">
         <x:v>束身衣</x:v>
       </x:c>
-      <x:c r="G17" s="6" t="str">
+      <x:c r="G17" s="8" t="str">
         <x:v>WhatsApp Image 2026-08-28 at 12.02.41 PM (4).jpeg</x:v>
       </x:c>
     </x:row>
